--- a/bench/data/files/synthetic6_C.xlsx
+++ b/bench/data/files/synthetic6_C.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N45"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -565,51 +565,55 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Mosaic GmbH</t>
+          <t>Echo Partners</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2011-06-16</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr"/>
+          <t>2012-12-14</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>2017-10-04</t>
+        </is>
+      </c>
       <c r="G5" s="4" t="n">
-        <v>334.1</v>
+        <v>1292</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v/>
+        <v>3969</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>89.7</v>
+        <v>312.1</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v/>
+        <v>493.7</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>142.8</v>
+        <v>348.2</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.858</v>
+        <v>0.249</v>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>Daniel Chen; Daniel Lopez; Thomas Chen; Sarah Gupta; Priya Yamamoto</t>
+          <t>Thomas Zhang; Jennifer Zhang</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -621,17 +625,17 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Vertex AG</t>
+          <t>Echo Labs</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -641,35 +645,35 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2010-03-20</t>
+          <t>2010-04-11</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2014-04-16</t>
+          <t>2018-03-31</t>
         </is>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1734.1</v>
+        <v>1391.4</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>2701.4</v>
+        <v>1291.8</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>165.5</v>
+        <v>254.8</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>353.4</v>
+        <v>312.5</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>569</v>
+        <v>528.8</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.381</v>
+        <v>0.523</v>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>Jessica Chen; Laura Nakamura; Robert Ueno; Thomas Ueno; Jessica Tanaka</t>
+          <t>Laura Lopez; Emma Brown; David Ivanov</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -681,17 +685,17 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Atlas Labs</t>
+          <t>Apex Group</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -701,35 +705,35 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2011-12-17</t>
+          <t>2012-03-24</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2017-03-14</t>
+          <t>2018-05-21</t>
         </is>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1341</v>
+        <v>1594.9</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1684.4</v>
+        <v>4080.3</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>146.7</v>
+        <v>294.7</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>178.5</v>
+        <v>505.5</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>583.5</v>
+        <v>514.8</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.878</v>
+        <v>0.956</v>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>Hannah Kim; Jessica Qureshi</t>
+          <t>Mark Hassan; Laura Davis</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -741,159 +745,159 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Nimbus Logistics</t>
+          <t>Indigo Health</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
+          <t>Denver, CO</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>2011-02-28</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-04</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>1836.8</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>2690.6</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>338.9</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>768.5</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>634.6</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>Rachel Chen; Christopher Gupta; Wei Evans; Mark Xu; Jessica Chen</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>Fund A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Helix Solutions</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
           <t>Chicago, IL</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>2010-04-08</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>2017-04-08</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>100.7</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>120.3</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="J8" s="4" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>0.648</v>
-      </c>
-      <c r="M8" s="4" t="inlineStr">
-        <is>
-          <t>Andrew Johnson; Amanda Johnson; Priya Ueno; Elena Vega; Sophie Vega</t>
-        </is>
-      </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>2013-04-22</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>2021-07-02</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>1128</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>3111.7</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>255.8</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>475.8</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>695.5</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>Elena Mueller; Rachel Kim; Laura Schmidt; Wei Evans</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>Fund A</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Fund A Average</t>
         </is>
       </c>
-      <c r="G9" s="6" t="n">
-        <v>877.5</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>1502</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>103.9</v>
-      </c>
-      <c r="J9" s="6" t="n">
-        <v>185.1</v>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>338.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Delta Pharma</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Denver, CO</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>2012-05-18</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>2018-03-26</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>1197.1</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>1796.6</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>199.7</v>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>271</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>211.5</v>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v>0.868</v>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
-        <is>
-          <t>Michael Williams; Matthew Kim; Ahmed Yamamoto; Mark Patel</t>
-        </is>
-      </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>Fund B</t>
-        </is>
+      <c r="G10" s="6" t="n">
+        <v>1448.6</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>3028.7</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>291.3</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>511.2</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>544.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Umbra Labs</t>
+          <t>Lumen Ltd</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -903,35 +907,35 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2013-10-01</t>
+          <t>2013-02-14</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2018-08-29</t>
+          <t>2016-11-26</t>
         </is>
       </c>
       <c r="G12" s="4" t="n">
-        <v>287.5</v>
+        <v>1937.2</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>217.5</v>
+        <v>6518.1</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>30.3</v>
+        <v>294</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>35.4</v>
+        <v>728.1</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>100</v>
+        <v>240.7</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.881</v>
+        <v>0.387</v>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>Jessica Evans; Elena Qureshi; James Evans; Andrew Ivanov; Andrew O'Brien</t>
+          <t>Daniel Yamamoto; Jennifer Lopez; Emma Zhang; Olivia Tanaka</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -943,17 +947,17 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Atlas Corp</t>
+          <t>Bloom Ltd</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Tokyo, JP</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -963,35 +967,35 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2013-12-26</t>
+          <t>2015-10-15</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2019-11-18</t>
+          <t>2019-11-28</t>
         </is>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1546.7</v>
+        <v>786.4</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3140</v>
+        <v>2222.3</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>209.5</v>
+        <v>131.5</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>401.8</v>
+        <v>169.9</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>142.3</v>
+        <v>378.9</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.399</v>
+        <v>0.654</v>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>Jennifer Chen; Ravi Xu; James Vega; Hannah Brown; Michael Chen</t>
+          <t>Jennifer Johnson; Sarah Vega; Rachel Anderson; Hannah Nakamura</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -1003,17 +1007,17 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Delta Ltd</t>
+          <t>Indigo Networks</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1023,35 +1027,35 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2015-08-11</t>
+          <t>2013-01-05</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2021-02-20</t>
         </is>
       </c>
       <c r="G14" s="4" t="n">
-        <v>641.4</v>
+        <v>1944.7</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2148.9</v>
+        <v>2562.9</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>178.1</v>
+        <v>225.9</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>216.1</v>
+        <v>540.1</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>629.4</v>
+        <v>558.2</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.929</v>
+        <v>0.576</v>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>Michael Schmidt; Michael Ivanov; Michael Schmidt; James Xu; Wei Gupta</t>
+          <t>James Evans; Olivia Williams; Ahmed Davis</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -1063,17 +1067,17 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Kepler Pharma</t>
+          <t>Vertex Industries</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1083,35 +1087,35 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>2014-08-01</t>
+          <t>2013-07-17</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2019-10-21</t>
+          <t>2017-04-20</t>
         </is>
       </c>
       <c r="G15" s="4" t="n">
-        <v>174.8</v>
+        <v>499.8</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>154.9</v>
+        <v>1347</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>32</v>
+        <v>107.2</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>66.59999999999999</v>
+        <v>144.6</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>134.1</v>
+        <v>480.7</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.593</v>
+        <v>0.331</v>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>Daniel Patel; Hannah Fischer; Christopher Evans</t>
+          <t>Mark Rossi; Wei Chen; Hannah Gupta; Amanda Rossi; Jessica Lopez</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -1123,17 +1127,17 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Ember Pharma</t>
+          <t>Umbra Systems</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1143,35 +1147,35 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2014-08-23</t>
+          <t>2013-08-13</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2018-08-20</t>
         </is>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1684.2</v>
+        <v>1921.3</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>4581.1</v>
+        <v>2787.8</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>334.7</v>
+        <v>211.4</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>814.1</v>
+        <v>514.5</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>231</v>
+        <v>317.1</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.219</v>
+        <v>0.896</v>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>Ahmed Ivanov; Michael Lopez; Matthew Vega</t>
+          <t>Sophie Hassan; Sarah Kim; Christopher Nakamura; Ahmed Johnson</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -1183,12 +1187,12 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Tessera Materials</t>
+          <t>Xenith Labs</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1203,35 +1207,35 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2014-02-17</t>
+          <t>2014-05-05</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>2017-12-03</t>
+          <t>2019-05-18</t>
         </is>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1738.3</v>
+        <v>153.2</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>3202.1</v>
+        <v>499.9</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>152.2</v>
+        <v>17.9</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>132.7</v>
+        <v>42.6</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>430.9</v>
+        <v>22.3</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.263</v>
+        <v>0.579</v>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>Andrew Ivanov; Sophie Ivanov; James Anderson; Andrew Schmidt</t>
+          <t>Jessica Nakamura; Emma Davis; David Qureshi; Mark Williams; Daniel Fischer</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -1241,161 +1245,161 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Radial Labs</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>New York, NY</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>2012-05-08</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>2017-03-25</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>1418.4</v>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>3699.2</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>303.2</v>
-      </c>
-      <c r="J18" s="4" t="n">
-        <v>694</v>
-      </c>
-      <c r="K18" s="4" t="n">
-        <v>196.1</v>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="M18" s="4" t="inlineStr">
-        <is>
-          <t>Robert Hassan; Wei Mueller; Laura Gupta; Sarah Nakamura</t>
-        </is>
-      </c>
-      <c r="N18" s="4" t="inlineStr">
-        <is>
-          <t>Fund B</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Cipher SA</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Seattle, WA</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>2012-10-13</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>2017-10-21</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>728.5</v>
-      </c>
-      <c r="H19" s="4" t="n">
-        <v>1721.4</v>
-      </c>
-      <c r="I19" s="4" t="n">
-        <v>148.6</v>
-      </c>
-      <c r="J19" s="4" t="n">
-        <v>320.9</v>
-      </c>
-      <c r="K19" s="4" t="n">
-        <v>166.8</v>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v>0.883</v>
-      </c>
-      <c r="M19" s="4" t="inlineStr">
-        <is>
-          <t>Daniel Davis; Emma Williams; Mark Evans; Christopher Rossi</t>
-        </is>
-      </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>Fund B</t>
-        </is>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Fund B Average</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>1207.1</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>2656.3</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>164.7</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>356.6</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>333</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Fund B Average</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>1046.3</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>2295.7</v>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>176.5</v>
-      </c>
-      <c r="J20" s="6" t="n">
-        <v>328.1</v>
-      </c>
-      <c r="K20" s="6" t="n">
-        <v>249.1</v>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Krypton Capital</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Toronto, CA</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>2016-03-10</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>1616.9</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>2716.3</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>393.3</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>496.9</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>1553.1</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>James Tanaka; Yuki Nakamura; Jennifer Williams; Yuki Chen; Olivia Zhang</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>Fund C</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Forge Industries</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Zurich, CH</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>2016-02-05</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>2024-04-05</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>567.9</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>1874.8</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>124.2</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>275.9</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>500.4</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>0.863</v>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>Yuki Johnson; Hannah Rossi; Laura Johnson</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>Fund C</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Vertex Pharma</t>
+          <t>Kepler Group</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1405,35 +1409,35 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2015-04-07</t>
+          <t>2016-03-21</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>2022-02-24</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="G22" s="4" t="n">
-        <v>731.8</v>
+        <v>1176.3</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2072.4</v>
+        <v>1834.6</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>125.4</v>
+        <v>172.7</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>201.3</v>
+        <v>145.4</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>66.5</v>
+        <v>217.5</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.281</v>
+        <v>0.245</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>Andrew Fischer; Andrew Schmidt; Ahmed Mueller; Matthew Yamamoto; Sarah Williams</t>
+          <t>Yuki Evans; Thomas Evans; Sophie Nakamura; Sarah Lopez</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -1445,12 +1449,12 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Mosaic Materials</t>
+          <t>Apex Health</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1465,35 +1469,35 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>2015-10-08</t>
+          <t>2017-12-05</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
+          <t>2021-01-31</t>
         </is>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1747.7</v>
+        <v>1989.3</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>4987.8</v>
+        <v>3819</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>197.8</v>
+        <v>277</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>481.4</v>
+        <v>495.1</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>677.4</v>
+        <v>675.2</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.749</v>
+        <v>0.398</v>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>James Chen; Christopher Williams</t>
+          <t>Jennifer Fischer; Matthew Patel</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -1505,17 +1509,17 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Fathom Energy</t>
+          <t>Halo AG</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1525,35 +1529,35 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2014-10-24</t>
+          <t>2014-06-11</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>2019-09-15</t>
+          <t>2019-08-12</t>
         </is>
       </c>
       <c r="G24" s="4" t="n">
-        <v>162.9</v>
+        <v>988</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>315.6</v>
+        <v>2070.4</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>40.9</v>
+        <v>232.6</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>77.09999999999999</v>
+        <v>553.3</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>102.6</v>
+        <v>750.6</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.729</v>
+        <v>0.931</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>Emma Qureshi; Ahmed Mueller; Hannah Qureshi; Amanda Davis</t>
+          <t>Andrew Chen; Robert Schmidt; Thomas Gupta; Elena Qureshi</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -1565,17 +1569,17 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Kepler Inc</t>
+          <t>Iris Corp</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1585,35 +1589,35 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>2015-11-05</t>
+          <t>2017-08-04</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>2020-10-24</t>
+          <t>2022-10-08</t>
         </is>
       </c>
       <c r="G25" s="4" t="n">
-        <v>68.5</v>
+        <v>1264.2</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>204.6</v>
+        <v>1705.8</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>8.1</v>
+        <v>117.3</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>17.5</v>
+        <v>194.3</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>32.8</v>
+        <v>229.2</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.761</v>
+        <v>0.833</v>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>Olivia Vega; Michael Qureshi; Robert Xu; Laura Evans; Elena Kim</t>
+          <t>Jennifer Xu; Christopher Chen; Christopher O'Brien; Amanda O'Brien</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -1625,17 +1629,17 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Atlas Energy</t>
+          <t>Meridian Industries</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1645,35 +1649,35 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2016-07-01</t>
+          <t>2017-10-09</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2020-11-02</t>
         </is>
       </c>
       <c r="G26" s="4" t="n">
-        <v>211.1</v>
+        <v>991.2</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>371.1</v>
+        <v>1571.7</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>57.4</v>
+        <v>152.8</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>68.2</v>
+        <v>376.1</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>159.7</v>
+        <v>516.9</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.473</v>
+        <v>0.411</v>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>Laura Brown; Jessica Patel; Jessica Vega; Matthew Fischer</t>
+          <t>Robert Anderson; Emma Davis</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -1685,17 +1689,17 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Gravity Capital</t>
+          <t>Iris Group</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1705,35 +1709,35 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>2015-09-18</t>
+          <t>2015-12-14</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>2023-06-22</t>
+          <t>2024-01-14</t>
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1783.5</v>
+        <v>1895.9</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2588</v>
+        <v>4946.4</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>261.4</v>
+        <v>374.4</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>221.8</v>
+        <v>891.4</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>739</v>
+        <v>234.8</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.342</v>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>Thomas Schmidt; Sarah O'Brien; Olivia Xu; Christopher Tanaka; Yuki Fischer</t>
+          <t>James Davis; David Tanaka; Amanda Davis; Thomas Brown; Daniel Schmidt</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -1743,101 +1747,101 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Tessera Logic</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Paris, FR</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>2015-03-06</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>2021-05-31</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>1704.6</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>3238</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>363.6</v>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>653.8</v>
+      </c>
+      <c r="K28" s="4" t="n">
+        <v>1283.6</v>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>0.952</v>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>Matthew Vega; Christopher Anderson; Hannah Hassan; Emma Evans; Wei Rossi</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>Fund C</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Fund C Average</t>
         </is>
       </c>
-      <c r="G28" s="6" t="n">
-        <v>784.2</v>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>1756.6</v>
-      </c>
-      <c r="I28" s="6" t="n">
-        <v>115.2</v>
-      </c>
-      <c r="J28" s="6" t="n">
-        <v>177.9</v>
-      </c>
-      <c r="K28" s="6" t="n">
-        <v>296.3</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Bloom Dynamics</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>New York, NY</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>2018-12-18</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>482.4</v>
-      </c>
-      <c r="H30" s="4" t="n">
-        <v>835.6</v>
-      </c>
-      <c r="I30" s="4" t="n">
-        <v>95</v>
-      </c>
-      <c r="J30" s="4" t="n">
-        <v>225.1</v>
-      </c>
-      <c r="K30" s="4" t="n">
-        <v>229</v>
-      </c>
-      <c r="L30" s="4" t="n">
-        <v>0.949</v>
-      </c>
-      <c r="M30" s="4" t="inlineStr">
-        <is>
-          <t>Christopher Mueller; Olivia Xu; Jessica Ivanov; David Schmidt</t>
-        </is>
-      </c>
-      <c r="N30" s="4" t="inlineStr">
-        <is>
-          <t>Fund D</t>
-        </is>
+      <c r="G29" s="6" t="n">
+        <v>1354.9</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>2641.9</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>245.3</v>
+      </c>
+      <c r="J29" s="6" t="n">
+        <v>453.6</v>
+      </c>
+      <c r="K29" s="6" t="n">
+        <v>662.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Stratus Pharma</t>
+          <t>Umbra Foods</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1847,35 +1851,35 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>2017-05-08</t>
+          <t>2019-03-01</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>2021-03-18</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1923.9</v>
+        <v>803.8</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>4821.3</v>
+        <v>646</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>206.4</v>
+        <v>106.2</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>446.1</v>
+        <v>97.8</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>566</v>
+        <v>153.1</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.582</v>
+        <v>0.866</v>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>Laura Chen; James Ueno; Sophie Johnson; Emma O'Brien; David Lopez</t>
+          <t>Wei Hassan; Matthew Johnson; James Fischer; Ahmed Rossi</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -1887,17 +1891,17 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Tessera Media</t>
+          <t>Glacier Pharma</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CA</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1907,35 +1911,35 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>2017-10-14</t>
+          <t>2017-05-22</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>2023-12-30</t>
+          <t>2020-02-24</t>
         </is>
       </c>
       <c r="G32" s="4" t="n">
-        <v>973</v>
+        <v>464.3</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1017.7</v>
+        <v>1372.2</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>95.90000000000001</v>
+        <v>101.6</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>187.3</v>
+        <v>158.1</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>117.7</v>
+        <v>108.7</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.233</v>
+        <v>0.573</v>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>Ravi Ueno; Emma Mueller; Andrew Rossi; Hannah Johnson</t>
+          <t>David Hassan; Sophie Fischer; Priya Nakamura; Jessica Brown</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -1947,7 +1951,7 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Ember Systems</t>
+          <t>Stratus Group</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -1957,45 +1961,41 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>2024-02-27</t>
-        </is>
-      </c>
+          <t>2019-07-28</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="n">
-        <v>1377.7</v>
+        <v>1552.5</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>3505.7</v>
+        <v/>
       </c>
       <c r="I33" s="4" t="n">
-        <v>148.5</v>
+        <v>207.9</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>225.6</v>
+        <v/>
       </c>
       <c r="K33" s="4" t="n">
-        <v>304.1</v>
+        <v>740.4</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.605</v>
+        <v>0.35</v>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>Ravi Ivanov; Emma Williams; Jessica Johnson; Yuki Rossi; Emma Zhang</t>
+          <t>Elena Ueno; Amanda Nakamura</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Gravity SA</t>
+          <t>Atlas SA</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2027,35 +2027,35 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>2019-01-27</t>
+          <t>2019-08-25</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1905.6</v>
+        <v>397.5</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>4541.1</v>
+        <v>995.9</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>277.2</v>
+        <v>59.3</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>484</v>
+        <v>132.4</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>1091.2</v>
+        <v>106.3</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.378</v>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>Priya Xu; Emma Zhang</t>
+          <t>Sarah Ueno; Ravi Evans; Daniel Schmidt; Matthew Schmidt</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -2067,17 +2067,17 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Fathom Tech</t>
+          <t>Yields Holdings</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CA</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2087,35 +2087,35 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2016-11-15</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="G35" s="4" t="n">
-        <v>1490.6</v>
+        <v>866.9</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>2811.3</v>
+        <v>772</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>378.6</v>
+        <v>111.4</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>312.3</v>
+        <v>139.2</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>686.3</v>
+        <v>217.7</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.797</v>
+        <v>0.476</v>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>Michael Kim; Emma Anderson; David Yamamoto; Sophie Yamamoto</t>
+          <t>Olivia Evans; Robert Mueller; Emma Anderson; Laura Schmidt</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -2131,73 +2131,69 @@
         </is>
       </c>
       <c r="G36" s="6" t="n">
-        <v>1358.9</v>
+        <v>817</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>2922.1</v>
+        <v>946.5</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>200.3</v>
+        <v>117.3</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>313.4</v>
+        <v>131.9</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>499.1</v>
+        <v>265.2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Cipher Logistics</t>
+          <t>Bloom Dynamics</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>2020-01-17</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>2025-01-13</t>
-        </is>
-      </c>
+          <t>2020-01-04</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="4" t="n">
-        <v>1198.8</v>
+        <v>1867.2</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>2207.1</v>
+        <v/>
       </c>
       <c r="I38" s="4" t="n">
-        <v>238</v>
+        <v>522.8</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>589.2</v>
+        <v/>
       </c>
       <c r="K38" s="4" t="n">
-        <v>709.7</v>
+        <v>453.8</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.351</v>
+        <v>0.233</v>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>Matthew Patel; Matthew Lopez</t>
+          <t>Daniel Brown; Olivia Tanaka</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr">
@@ -2209,55 +2205,51 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Echo Networks</t>
+          <t>Gravity Tech</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>2021-01-08</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>2025-01-24</t>
-        </is>
-      </c>
+          <t>2020-09-22</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="4" t="n">
-        <v>808.4</v>
+        <v>746.5</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>650.7</v>
+        <v/>
       </c>
       <c r="I39" s="4" t="n">
-        <v>201.1</v>
+        <v>72.3</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>317.1</v>
+        <v/>
       </c>
       <c r="K39" s="4" t="n">
-        <v>585.1</v>
+        <v>143.1</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>Sarah Patel; Thomas Lopez; Priya Gupta</t>
+          <t>Sophie Davis; Daniel Johnson; Matthew Ivanov; Ahmed O'Brien; Amanda Chen</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -2269,12 +2261,12 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Ember Tech</t>
+          <t>Ember Solutions</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2289,35 +2281,35 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>2021-04-26</t>
+          <t>2019-08-13</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="G40" s="4" t="n">
-        <v>173.3</v>
+        <v>1400.8</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>148</v>
+        <v>2921.7</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>14.9</v>
+        <v>150.9</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>31.4</v>
+        <v>360</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>26.4</v>
+        <v>146.6</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.23</v>
+        <v>0.773</v>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>Wei Davis; David Chen; Rachel Lopez</t>
+          <t>Ravi Gupta; Sophie Anderson; Jennifer Yamamoto; Sarah Zhang</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -2329,17 +2321,17 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Fathom Logistics</t>
+          <t>Quanta Ltd</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2349,35 +2341,35 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>2019-03-26</t>
+          <t>2018-06-03</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2022-04-26</t>
         </is>
       </c>
       <c r="G41" s="4" t="n">
-        <v>1876.4</v>
+        <v>602.3</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>6471.2</v>
+        <v>736.6</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>402.1</v>
+        <v>81.3</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>699.5</v>
+        <v>163.8</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>608.1</v>
+        <v>271.5</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>0.316</v>
+        <v>0.59</v>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>Sophie Fischer; Amanda Zhang</t>
+          <t>Ravi Nakamura; Mark Lopez; Jennifer Chen</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -2389,17 +2381,17 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Vertex Energy</t>
+          <t>Forge Networks</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2409,35 +2401,35 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2020-10-27</t>
+          <t>2018-04-21</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2022-05-05</t>
         </is>
       </c>
       <c r="G42" s="4" t="n">
-        <v>151</v>
+        <v>1481.5</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>299.8</v>
+        <v>1961.3</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>32.3</v>
+        <v>155.4</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>55.1</v>
+        <v>232.3</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>124.2</v>
+        <v>606.9</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>0.415</v>
+        <v>0.784</v>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>Jennifer Schmidt; Amanda Chen; Sarah Hassan</t>
+          <t>Laura Tanaka; Sarah Lopez; Amanda Mueller; Ravi Gupta</t>
         </is>
       </c>
       <c r="N42" s="4" t="inlineStr">
@@ -2449,17 +2441,17 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Beacon Materials</t>
+          <t>Yields AG</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2469,35 +2461,35 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>2021-10-22</t>
+          <t>2021-09-26</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="G43" s="4" t="n">
-        <v>1433.8</v>
+        <v>576.5</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>3263.9</v>
+        <v>685.9</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>132.9</v>
+        <v>133.7</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>205.3</v>
+        <v>151.6</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>223.2</v>
+        <v>304.1</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>0.666</v>
+        <v>0.318</v>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>Elena Xu; Priya Gupta; Olivia Davis</t>
+          <t>David Williams; Yuki Vega; Sarah O'Brien; Thomas Nakamura; Laura Williams</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -2509,55 +2501,51 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Forge AG</t>
+          <t>Umbra Inc</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>2021-04-08</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>2025-01-13</t>
-        </is>
-      </c>
+          <t>2021-11-12</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr"/>
       <c r="G44" s="4" t="n">
-        <v>990.7</v>
+        <v>1901.4</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>1747</v>
+        <v/>
       </c>
       <c r="I44" s="4" t="n">
-        <v>93.59999999999999</v>
+        <v>306.2</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>180.2</v>
+        <v/>
       </c>
       <c r="K44" s="4" t="n">
-        <v>337.3</v>
+        <v>314.2</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.651</v>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>Emma Hassan; Jessica Hassan; Wei O'Brien; Rachel Vega</t>
+          <t>Yuki Williams; Elena Fischer</t>
         </is>
       </c>
       <c r="N44" s="4" t="inlineStr">
@@ -2567,25 +2555,85 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Glacier Holdings</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>2019-10-02</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>1038.5</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>2125.1</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>256.9</v>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>505.8</v>
+      </c>
+      <c r="K45" s="4" t="n">
+        <v>1050.9</v>
+      </c>
+      <c r="L45" s="4" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="M45" s="4" t="inlineStr">
+        <is>
+          <t>Priya Chen; Mark Mueller; Yuki Williams; Olivia Qureshi</t>
+        </is>
+      </c>
+      <c r="N45" s="4" t="inlineStr">
+        <is>
+          <t>Fund E</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>Fund E Average</t>
         </is>
       </c>
-      <c r="G45" s="6" t="n">
-        <v>947.5</v>
-      </c>
-      <c r="H45" s="6" t="n">
-        <v>2112.5</v>
-      </c>
-      <c r="I45" s="6" t="n">
-        <v>159.3</v>
-      </c>
-      <c r="J45" s="6" t="n">
-        <v>296.8</v>
-      </c>
-      <c r="K45" s="6" t="n">
-        <v>373.4</v>
+      <c r="G46" s="6" t="n">
+        <v>1201.8</v>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>1686.1</v>
+      </c>
+      <c r="I46" s="6" t="n">
+        <v>209.9</v>
+      </c>
+      <c r="J46" s="6" t="n">
+        <v>282.7</v>
+      </c>
+      <c r="K46" s="6" t="n">
+        <v>411.4</v>
       </c>
     </row>
   </sheetData>
